--- a/code/cod_algorithm/a_02_COD Coding Input template.xlsx
+++ b/code/cod_algorithm/a_02_COD Coding Input template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Desktop/mortality_data_test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Documents/GitHub/harmonized_carceral_mortality_data/code/cod_algorithm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61A41344-7737-6B42-8E05-D7B28F54FBE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0675540-3EDE-2B42-8F02-3320F6FBFE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="15440" xr2:uid="{0541AF24-24CC-0E4B-9FFF-D461BEE0225D}"/>
   </bookViews>
@@ -36,12 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>CASE_NUMBER</t>
-  </si>
-  <si>
-    <t>MANNER</t>
   </si>
   <si>
     <t>CAUSE</t>
@@ -449,22 +446,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FFDB6B2-6710-6548-90BD-FC1636CEF290}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="77.83203125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="77.83203125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
